--- a/artfynd/A 20367-2025 artfynd.xlsx
+++ b/artfynd/A 20367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,48 +789,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124671087</v>
+        <v>136716335</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>89316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4404</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkliden, Vb</t>
+          <t>Lundaliden-Falkliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778140</v>
+        <v>778368</v>
       </c>
       <c r="R3" t="n">
-        <v>7191913</v>
+        <v>7191875</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,24 +884,28 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124671087</t>
+          <t>https://artportalen.se/Sighting/136716335</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124671088</v>
+        <v>124671087</v>
       </c>
       <c r="B4" t="n">
         <v>99118</v>
@@ -926,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778096</v>
+        <v>778140</v>
       </c>
       <c r="R4" t="n">
-        <v>7191916</v>
+        <v>7191913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,13 +1001,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124671088</t>
+          <t>https://artportalen.se/Sighting/124671087</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124671089</v>
+        <v>124671088</v>
       </c>
       <c r="B5" t="n">
         <v>99118</v>
@@ -1028,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778084</v>
+        <v>778096</v>
       </c>
       <c r="R5" t="n">
-        <v>7191928</v>
+        <v>7191916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,13 +1103,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124671089</t>
+          <t>https://artportalen.se/Sighting/124671088</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124799559</v>
+        <v>124671089</v>
       </c>
       <c r="B6" t="n">
         <v>99118</v>
@@ -1126,14 +1140,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rötmyran, Vb</t>
+          <t>Falkliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778070</v>
+        <v>778084</v>
       </c>
       <c r="R6" t="n">
-        <v>7191845</v>
+        <v>7191928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,24 +1194,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124799559</t>
+          <t>https://artportalen.se/Sighting/124671089</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125013936</v>
+        <v>124799559</v>
       </c>
       <c r="B7" t="n">
         <v>99118</v>
@@ -1226,24 +1240,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lundliden, Vb</t>
+          <t>Rötmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>778058</v>
+        <v>778070</v>
       </c>
       <c r="R7" t="n">
-        <v>7191907</v>
+        <v>7191845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,31 +1290,30 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125013936</t>
+          <t>https://artportalen.se/Sighting/124799559</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125014012</v>
+        <v>125013936</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>778079</v>
+        <v>778058</v>
       </c>
       <c r="R8" t="n">
-        <v>7191921</v>
+        <v>7191907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,13 +1418,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125014012</t>
+          <t>https://artportalen.se/Sighting/125013936</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125014041</v>
+        <v>125014012</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>778113</v>
+        <v>778079</v>
       </c>
       <c r="R9" t="n">
-        <v>7191912</v>
+        <v>7191921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1529,234 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/125014012</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125014041</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lundliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>778113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7191912</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/125014041</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136716338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106487</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lundaliden-Falkliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>778452</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7191849</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136716338</t>
         </is>
       </c>
     </row>
@@ -1538,6 +1770,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20367-2025 artfynd.xlsx
+++ b/artfynd/A 20367-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>136716335</v>
       </c>
       <c r="B3" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136716338</v>
       </c>
       <c r="B11" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
